--- a/output/pdf_financials_xlsx/FMR.xlsx
+++ b/output/pdf_financials_xlsx/FMR.xlsx
@@ -4444,37 +4444,37 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>-0.159172</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.570408</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.468006</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.083</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.928993</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.723596</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.623618</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.061858</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.931213</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.977623</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.973288</v>
       </c>
     </row>
     <row r="93">
@@ -7336,7 +7336,11 @@
           <t>Share-based payment reserve 10</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -8596,7 +8600,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -9028,7 +9036,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -9474,7 +9486,11 @@
           <t>Share-based payment reserve 12</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -10546,7 +10562,11 @@
           <t>Share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FMR.xlsx
+++ b/output/pdf_financials_xlsx/FMR.xlsx
@@ -879,40 +879,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000508</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.241411</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.291099</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.01758</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.04077</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.025225</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.121998</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.210699</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.023165</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.020181</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003971</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-3e-06</v>
       </c>
     </row>
     <row r="13">
@@ -1586,40 +1586,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.012732</v>
+        <v>-0.012224</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.172401</v>
+        <v>-4.93099</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.048557</v>
+        <v>2.339656</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.926289</v>
+        <v>-4.908709</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>13.31807</v>
+        <v>13.35884</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-21.82677</v>
+        <v>-21.801545</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.805466</v>
+        <v>0.927464</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.950805</v>
+        <v>-1.740106</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-12.057828</v>
+        <v>-12.034663</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-5.682322</v>
+        <v>-5.662141</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.726512</v>
+        <v>-2.722541</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.614776</v>
+        <v>-2.614773</v>
       </c>
     </row>
     <row r="28">
@@ -1672,40 +1672,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.012732</v>
+        <v>-0.012224</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.172401</v>
+        <v>-4.93099</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.048557</v>
+        <v>2.339656</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.926289</v>
+        <v>-4.908709</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>13.31807</v>
+        <v>13.35884</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-21.82677</v>
+        <v>-21.801545</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.805466</v>
+        <v>0.927464</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.950805</v>
+        <v>-1.740106</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-12.057828</v>
+        <v>-12.034663</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.682322</v>
+        <v>-5.662141</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.726512</v>
+        <v>-2.722541</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.614776</v>
+        <v>-2.614773</v>
       </c>
     </row>
     <row r="30">
@@ -1917,22 +1917,22 @@
         <v>0.077749</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.205011</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.201235</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.163161</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.035084</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.055661</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.085855</v>
       </c>
     </row>
     <row r="35">
@@ -2003,22 +2003,22 @@
         <v>0.077749</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.205011</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.201235</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.163161</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.035084</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.055661</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.085855</v>
       </c>
     </row>
     <row r="37">
@@ -2519,22 +2519,22 @@
         <v>12.534548</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>13.725059</v>
+        <v>13.520048</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>12.262651</v>
+        <v>12.061416</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>8.922444</v>
+        <v>8.759283</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.47133</v>
+        <v>3.436246</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.393043</v>
+        <v>2.337382</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.825634</v>
+        <v>0.739779</v>
       </c>
     </row>
     <row r="49">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E203" s="5" t="n">
@@ -21216,7 +21216,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -23716,7 +23716,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -26858,7 +26858,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">

--- a/output/pdf_financials_xlsx/FMR.xlsx
+++ b/output/pdf_financials_xlsx/FMR.xlsx
@@ -5397,37 +5397,37 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.830395</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>7.973426</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>7.658222</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>8.658806</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>8.777155</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>9.303388</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>5.673314</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>2.899442</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>1.466325</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.270765</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.186458</v>
       </c>
     </row>
     <row r="116">
@@ -11884,7 +11884,11 @@
           <t>Proceeds from sale of investments 5</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -13164,7 +13168,11 @@
           <t>Proceeds from private placement 9</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -14074,7 +14082,11 @@
           <t>Proceeds from sale of investments 6</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -14526,7 +14538,11 @@
           <t>Deferred inocme tax recovery</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -14900,7 +14916,11 @@
           <t>Proceeds from private placement 8</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -16288,7 +16308,11 @@
           <t>Proceeds from sale of investments 5, 7</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -20350,7 +20374,11 @@
           <t>Proceeds from sale of investments 7</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
